--- a/test/dati/estratto-conto.xlsx
+++ b/test/dati/estratto-conto.xlsx
@@ -411,10 +411,11 @@
       <c r="B6" s="1">
         <v>46235</v>
       </c>
+      <c/>
       <c r="D6">
         <v>1850</v>
       </c>
-      <c r="E6" t="s">
+      <c t="s">
         <v>9</v>
       </c>
     </row>
@@ -428,7 +429,8 @@
       <c r="C7">
         <v>700</v>
       </c>
-      <c r="E7" t="s">
+      <c/>
+      <c t="s">
         <v>10</v>
       </c>
     </row>
@@ -442,7 +444,8 @@
       <c r="C8">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
+      <c/>
+      <c t="s">
         <v>11</v>
       </c>
     </row>
@@ -456,7 +459,8 @@
       <c r="C9">
         <v>61.2</v>
       </c>
-      <c r="E9" t="s">
+      <c/>
+      <c t="s">
         <v>12</v>
       </c>
     </row>
@@ -470,7 +474,8 @@
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="E10" t="s">
+      <c/>
+      <c t="s">
         <v>13</v>
       </c>
     </row>
@@ -484,7 +489,8 @@
       <c r="C11">
         <v>3.5</v>
       </c>
-      <c r="E11" t="s">
+      <c/>
+      <c t="s">
         <v>14</v>
       </c>
     </row>
@@ -498,7 +504,8 @@
       <c r="C12">
         <v>63.03</v>
       </c>
-      <c r="E12" t="s">
+      <c/>
+      <c t="s">
         <v>15</v>
       </c>
     </row>
@@ -512,7 +519,8 @@
       <c r="C13">
         <v>19</v>
       </c>
-      <c r="E13" t="s">
+      <c/>
+      <c t="s">
         <v>16</v>
       </c>
     </row>
@@ -526,7 +534,8 @@
       <c r="C14">
         <v>17.98</v>
       </c>
-      <c r="E14" t="s">
+      <c/>
+      <c t="s">
         <v>17</v>
       </c>
     </row>
@@ -540,7 +549,8 @@
       <c r="C15">
         <v>34.5</v>
       </c>
-      <c r="E15" t="s">
+      <c/>
+      <c t="s">
         <v>18</v>
       </c>
     </row>
@@ -554,7 +564,8 @@
       <c r="C16">
         <v>17</v>
       </c>
-      <c r="E16" t="s">
+      <c/>
+      <c t="s">
         <v>19</v>
       </c>
     </row>
@@ -568,7 +579,8 @@
       <c r="C17">
         <v>15.9</v>
       </c>
-      <c r="E17" t="s">
+      <c/>
+      <c t="s">
         <v>20</v>
       </c>
     </row>
@@ -582,7 +594,8 @@
       <c r="C18">
         <v>39.32</v>
       </c>
-      <c r="E18" t="s">
+      <c/>
+      <c t="s">
         <v>21</v>
       </c>
     </row>
@@ -596,7 +609,8 @@
       <c r="C19">
         <v>52.41</v>
       </c>
-      <c r="E19" t="s">
+      <c/>
+      <c t="s">
         <v>22</v>
       </c>
     </row>
@@ -610,7 +624,8 @@
       <c r="C20">
         <v>4</v>
       </c>
-      <c r="E20" t="s">
+      <c/>
+      <c t="s">
         <v>23</v>
       </c>
     </row>
@@ -624,7 +639,8 @@
       <c r="C21">
         <v>3.5</v>
       </c>
-      <c r="E21" t="s">
+      <c/>
+      <c t="s">
         <v>24</v>
       </c>
     </row>
@@ -638,7 +654,8 @@
       <c r="C22">
         <v>63.03</v>
       </c>
-      <c r="E22" t="s">
+      <c/>
+      <c t="s">
         <v>25</v>
       </c>
     </row>
@@ -652,7 +669,8 @@
       <c r="C23">
         <v>19</v>
       </c>
-      <c r="E23" t="s">
+      <c/>
+      <c t="s">
         <v>26</v>
       </c>
     </row>
@@ -666,7 +684,8 @@
       <c r="C24">
         <v>17.98</v>
       </c>
-      <c r="E24" t="s">
+      <c/>
+      <c t="s">
         <v>27</v>
       </c>
     </row>
@@ -680,7 +699,8 @@
       <c r="C25">
         <v>34.5</v>
       </c>
-      <c r="E25" t="s">
+      <c/>
+      <c t="s">
         <v>28</v>
       </c>
     </row>
@@ -694,7 +714,8 @@
       <c r="C26">
         <v>17</v>
       </c>
-      <c r="E26" t="s">
+      <c/>
+      <c t="s">
         <v>29</v>
       </c>
     </row>
@@ -708,7 +729,8 @@
       <c r="C27">
         <v>15.9</v>
       </c>
-      <c r="E27" t="s">
+      <c/>
+      <c t="s">
         <v>30</v>
       </c>
     </row>
@@ -722,7 +744,8 @@
       <c r="C28">
         <v>39.32</v>
       </c>
-      <c r="E28" t="s">
+      <c/>
+      <c t="s">
         <v>31</v>
       </c>
     </row>
@@ -736,7 +759,8 @@
       <c r="C29">
         <v>52.41</v>
       </c>
-      <c r="E29" t="s">
+      <c/>
+      <c t="s">
         <v>32</v>
       </c>
     </row>
@@ -750,7 +774,8 @@
       <c r="C30">
         <v>4</v>
       </c>
-      <c r="E30" t="s">
+      <c/>
+      <c t="s">
         <v>33</v>
       </c>
     </row>
@@ -764,7 +789,8 @@
       <c r="C31">
         <v>3.5</v>
       </c>
-      <c r="E31" t="s">
+      <c/>
+      <c t="s">
         <v>34</v>
       </c>
     </row>
@@ -778,7 +804,8 @@
       <c r="C32">
         <v>63.03</v>
       </c>
-      <c r="E32" t="s">
+      <c/>
+      <c t="s">
         <v>35</v>
       </c>
     </row>
@@ -792,7 +819,8 @@
       <c r="C33">
         <v>19</v>
       </c>
-      <c r="E33" t="s">
+      <c/>
+      <c t="s">
         <v>36</v>
       </c>
     </row>
@@ -806,7 +834,8 @@
       <c r="C34">
         <v>17.98</v>
       </c>
-      <c r="E34" t="s">
+      <c/>
+      <c t="s">
         <v>37</v>
       </c>
     </row>
@@ -820,7 +849,8 @@
       <c r="C35">
         <v>34.5</v>
       </c>
-      <c r="E35" t="s">
+      <c/>
+      <c t="s">
         <v>38</v>
       </c>
     </row>
@@ -834,7 +864,8 @@
       <c r="C36">
         <v>17</v>
       </c>
-      <c r="E36" t="s">
+      <c/>
+      <c t="s">
         <v>39</v>
       </c>
     </row>
@@ -848,7 +879,8 @@
       <c r="C37">
         <v>15.9</v>
       </c>
-      <c r="E37" t="s">
+      <c/>
+      <c t="s">
         <v>40</v>
       </c>
     </row>
@@ -862,7 +894,8 @@
       <c r="C38">
         <v>39.32</v>
       </c>
-      <c r="E38" t="s">
+      <c/>
+      <c t="s">
         <v>41</v>
       </c>
     </row>
@@ -876,7 +909,8 @@
       <c r="C39">
         <v>52.41</v>
       </c>
-      <c r="E39" t="s">
+      <c/>
+      <c t="s">
         <v>42</v>
       </c>
     </row>
@@ -890,7 +924,8 @@
       <c r="C40">
         <v>4</v>
       </c>
-      <c r="E40" t="s">
+      <c/>
+      <c t="s">
         <v>43</v>
       </c>
     </row>
@@ -904,7 +939,8 @@
       <c r="C41">
         <v>3.5</v>
       </c>
-      <c r="E41" t="s">
+      <c/>
+      <c t="s">
         <v>44</v>
       </c>
     </row>
@@ -918,7 +954,8 @@
       <c r="C42">
         <v>63.03</v>
       </c>
-      <c r="E42" t="s">
+      <c/>
+      <c t="s">
         <v>45</v>
       </c>
     </row>
@@ -932,7 +969,8 @@
       <c r="C43">
         <v>19</v>
       </c>
-      <c r="E43" t="s">
+      <c/>
+      <c t="s">
         <v>46</v>
       </c>
     </row>
@@ -946,7 +984,8 @@
       <c r="C44">
         <v>17.98</v>
       </c>
-      <c r="E44" t="s">
+      <c/>
+      <c t="s">
         <v>47</v>
       </c>
     </row>
@@ -960,7 +999,8 @@
       <c r="C45">
         <v>34.5</v>
       </c>
-      <c r="E45" t="s">
+      <c/>
+      <c t="s">
         <v>48</v>
       </c>
     </row>
@@ -974,7 +1014,8 @@
       <c r="C46">
         <v>17</v>
       </c>
-      <c r="E46" t="s">
+      <c/>
+      <c t="s">
         <v>49</v>
       </c>
     </row>
@@ -988,7 +1029,8 @@
       <c r="C47">
         <v>15.9</v>
       </c>
-      <c r="E47" t="s">
+      <c/>
+      <c t="s">
         <v>50</v>
       </c>
     </row>
@@ -1002,7 +1044,8 @@
       <c r="C48">
         <v>39.32</v>
       </c>
-      <c r="E48" t="s">
+      <c/>
+      <c t="s">
         <v>51</v>
       </c>
     </row>
@@ -1016,7 +1059,8 @@
       <c r="C49">
         <v>52.41</v>
       </c>
-      <c r="E49" t="s">
+      <c/>
+      <c t="s">
         <v>52</v>
       </c>
     </row>
@@ -1030,7 +1074,8 @@
       <c r="C50">
         <v>4</v>
       </c>
-      <c r="E50" t="s">
+      <c/>
+      <c t="s">
         <v>53</v>
       </c>
     </row>
@@ -1044,7 +1089,8 @@
       <c r="C51">
         <v>3.5</v>
       </c>
-      <c r="E51" t="s">
+      <c/>
+      <c t="s">
         <v>54</v>
       </c>
     </row>
@@ -1058,7 +1104,8 @@
       <c r="C52">
         <v>63.03</v>
       </c>
-      <c r="E52" t="s">
+      <c/>
+      <c t="s">
         <v>55</v>
       </c>
     </row>
@@ -1072,7 +1119,8 @@
       <c r="C53">
         <v>19</v>
       </c>
-      <c r="E53" t="s">
+      <c/>
+      <c t="s">
         <v>56</v>
       </c>
     </row>
@@ -1086,7 +1134,8 @@
       <c r="C54">
         <v>17.98</v>
       </c>
-      <c r="E54" t="s">
+      <c/>
+      <c t="s">
         <v>57</v>
       </c>
     </row>
@@ -1100,7 +1149,8 @@
       <c r="C55">
         <v>34.5</v>
       </c>
-      <c r="E55" t="s">
+      <c/>
+      <c t="s">
         <v>58</v>
       </c>
     </row>
@@ -1114,7 +1164,8 @@
       <c r="C56">
         <v>17</v>
       </c>
-      <c r="E56" t="s">
+      <c/>
+      <c t="s">
         <v>59</v>
       </c>
     </row>
@@ -1128,7 +1179,8 @@
       <c r="C57">
         <v>15.9</v>
       </c>
-      <c r="E57" t="s">
+      <c/>
+      <c t="s">
         <v>60</v>
       </c>
     </row>
@@ -1142,7 +1194,8 @@
       <c r="C58">
         <v>39.32</v>
       </c>
-      <c r="E58" t="s">
+      <c/>
+      <c t="s">
         <v>61</v>
       </c>
     </row>
@@ -1156,7 +1209,8 @@
       <c r="C59">
         <v>52.41</v>
       </c>
-      <c r="E59" t="s">
+      <c/>
+      <c t="s">
         <v>62</v>
       </c>
     </row>
@@ -1170,7 +1224,8 @@
       <c r="C60">
         <v>4</v>
       </c>
-      <c r="E60" t="s">
+      <c/>
+      <c t="s">
         <v>63</v>
       </c>
     </row>
@@ -1184,7 +1239,8 @@
       <c r="C61">
         <v>3.5</v>
       </c>
-      <c r="E61" t="s">
+      <c/>
+      <c t="s">
         <v>64</v>
       </c>
     </row>
@@ -1198,7 +1254,8 @@
       <c r="C62">
         <v>63.03</v>
       </c>
-      <c r="E62" t="s">
+      <c/>
+      <c t="s">
         <v>65</v>
       </c>
     </row>
@@ -1212,7 +1269,8 @@
       <c r="C63">
         <v>19</v>
       </c>
-      <c r="E63" t="s">
+      <c/>
+      <c t="s">
         <v>66</v>
       </c>
     </row>
@@ -1226,7 +1284,8 @@
       <c r="C64">
         <v>17.98</v>
       </c>
-      <c r="E64" t="s">
+      <c/>
+      <c t="s">
         <v>67</v>
       </c>
     </row>
@@ -1240,7 +1299,8 @@
       <c r="C65">
         <v>34.5</v>
       </c>
-      <c r="E65" t="s">
+      <c/>
+      <c t="s">
         <v>68</v>
       </c>
     </row>
@@ -1254,7 +1314,8 @@
       <c r="C66">
         <v>17</v>
       </c>
-      <c r="E66" t="s">
+      <c/>
+      <c t="s">
         <v>69</v>
       </c>
     </row>
@@ -1268,7 +1329,8 @@
       <c r="C67">
         <v>15.9</v>
       </c>
-      <c r="E67" t="s">
+      <c/>
+      <c t="s">
         <v>70</v>
       </c>
     </row>
@@ -1282,7 +1344,8 @@
       <c r="C68">
         <v>39.32</v>
       </c>
-      <c r="E68" t="s">
+      <c/>
+      <c t="s">
         <v>71</v>
       </c>
     </row>
@@ -1296,7 +1359,8 @@
       <c r="C69">
         <v>52.41</v>
       </c>
-      <c r="E69" t="s">
+      <c/>
+      <c t="s">
         <v>72</v>
       </c>
     </row>
@@ -1310,7 +1374,8 @@
       <c r="C70">
         <v>4</v>
       </c>
-      <c r="E70" t="s">
+      <c/>
+      <c t="s">
         <v>73</v>
       </c>
     </row>
@@ -1324,7 +1389,8 @@
       <c r="C71">
         <v>3.5</v>
       </c>
-      <c r="E71" t="s">
+      <c/>
+      <c t="s">
         <v>74</v>
       </c>
     </row>
@@ -1338,7 +1404,8 @@
       <c r="C72">
         <v>63.03</v>
       </c>
-      <c r="E72" t="s">
+      <c/>
+      <c t="s">
         <v>75</v>
       </c>
     </row>
@@ -1352,7 +1419,8 @@
       <c r="C73">
         <v>19</v>
       </c>
-      <c r="E73" t="s">
+      <c/>
+      <c t="s">
         <v>76</v>
       </c>
     </row>
@@ -1366,7 +1434,8 @@
       <c r="C74">
         <v>17.98</v>
       </c>
-      <c r="E74" t="s">
+      <c/>
+      <c t="s">
         <v>77</v>
       </c>
     </row>
@@ -1380,7 +1449,8 @@
       <c r="C75">
         <v>34.5</v>
       </c>
-      <c r="E75" t="s">
+      <c/>
+      <c t="s">
         <v>78</v>
       </c>
     </row>
@@ -1394,7 +1464,8 @@
       <c r="C76">
         <v>17</v>
       </c>
-      <c r="E76" t="s">
+      <c/>
+      <c t="s">
         <v>79</v>
       </c>
     </row>
@@ -1408,7 +1479,8 @@
       <c r="C77">
         <v>15.9</v>
       </c>
-      <c r="E77" t="s">
+      <c/>
+      <c t="s">
         <v>80</v>
       </c>
     </row>
@@ -1422,7 +1494,8 @@
       <c r="C78">
         <v>39.32</v>
       </c>
-      <c r="E78" t="s">
+      <c/>
+      <c t="s">
         <v>81</v>
       </c>
     </row>
@@ -1436,7 +1509,8 @@
       <c r="C79">
         <v>52.41</v>
       </c>
-      <c r="E79" t="s">
+      <c/>
+      <c t="s">
         <v>82</v>
       </c>
     </row>
@@ -1450,7 +1524,8 @@
       <c r="C80">
         <v>4</v>
       </c>
-      <c r="E80" t="s">
+      <c/>
+      <c t="s">
         <v>83</v>
       </c>
     </row>
@@ -1464,7 +1539,8 @@
       <c r="C81">
         <v>3.5</v>
       </c>
-      <c r="E81" t="s">
+      <c/>
+      <c t="s">
         <v>84</v>
       </c>
     </row>
@@ -1478,7 +1554,8 @@
       <c r="C82">
         <v>63.03</v>
       </c>
-      <c r="E82" t="s">
+      <c/>
+      <c t="s">
         <v>85</v>
       </c>
     </row>
@@ -1492,7 +1569,8 @@
       <c r="C83">
         <v>19</v>
       </c>
-      <c r="E83" t="s">
+      <c/>
+      <c t="s">
         <v>86</v>
       </c>
     </row>
@@ -1506,7 +1584,8 @@
       <c r="C84">
         <v>17.98</v>
       </c>
-      <c r="E84" t="s">
+      <c/>
+      <c t="s">
         <v>87</v>
       </c>
     </row>
@@ -1520,7 +1599,8 @@
       <c r="C85">
         <v>34.5</v>
       </c>
-      <c r="E85" t="s">
+      <c/>
+      <c t="s">
         <v>88</v>
       </c>
     </row>
@@ -1534,7 +1614,8 @@
       <c r="C86">
         <v>17</v>
       </c>
-      <c r="E86" t="s">
+      <c/>
+      <c t="s">
         <v>89</v>
       </c>
     </row>
@@ -1548,7 +1629,8 @@
       <c r="C87">
         <v>15.9</v>
       </c>
-      <c r="E87" t="s">
+      <c/>
+      <c t="s">
         <v>90</v>
       </c>
     </row>
@@ -1562,7 +1644,8 @@
       <c r="C88">
         <v>39.32</v>
       </c>
-      <c r="E88" t="s">
+      <c/>
+      <c t="s">
         <v>91</v>
       </c>
     </row>
@@ -1576,7 +1659,8 @@
       <c r="C89">
         <v>52.41</v>
       </c>
-      <c r="E89" t="s">
+      <c/>
+      <c t="s">
         <v>92</v>
       </c>
     </row>
@@ -1590,7 +1674,8 @@
       <c r="C90">
         <v>4</v>
       </c>
-      <c r="E90" t="s">
+      <c/>
+      <c t="s">
         <v>93</v>
       </c>
     </row>
@@ -1604,7 +1689,8 @@
       <c r="C91">
         <v>3.5</v>
       </c>
-      <c r="E91" t="s">
+      <c/>
+      <c t="s">
         <v>94</v>
       </c>
     </row>
@@ -1618,7 +1704,8 @@
       <c r="C92">
         <v>63.03</v>
       </c>
-      <c r="E92" t="s">
+      <c/>
+      <c t="s">
         <v>95</v>
       </c>
     </row>
@@ -1632,7 +1719,8 @@
       <c r="C93">
         <v>19</v>
       </c>
-      <c r="E93" t="s">
+      <c/>
+      <c t="s">
         <v>96</v>
       </c>
     </row>
@@ -1646,7 +1734,8 @@
       <c r="C94">
         <v>17.98</v>
       </c>
-      <c r="E94" t="s">
+      <c/>
+      <c t="s">
         <v>97</v>
       </c>
     </row>
@@ -1660,7 +1749,8 @@
       <c r="C95">
         <v>34.5</v>
       </c>
-      <c r="E95" t="s">
+      <c/>
+      <c t="s">
         <v>98</v>
       </c>
     </row>
@@ -1674,7 +1764,8 @@
       <c r="C96">
         <v>17</v>
       </c>
-      <c r="E96" t="s">
+      <c/>
+      <c t="s">
         <v>99</v>
       </c>
     </row>
@@ -1688,7 +1779,8 @@
       <c r="C97">
         <v>15.9</v>
       </c>
-      <c r="E97" t="s">
+      <c/>
+      <c t="s">
         <v>100</v>
       </c>
     </row>
@@ -1702,7 +1794,8 @@
       <c r="C98">
         <v>39.32</v>
       </c>
-      <c r="E98" t="s">
+      <c/>
+      <c t="s">
         <v>101</v>
       </c>
     </row>
@@ -1716,7 +1809,8 @@
       <c r="C99">
         <v>52.41</v>
       </c>
-      <c r="E99" t="s">
+      <c/>
+      <c t="s">
         <v>102</v>
       </c>
     </row>
@@ -1730,7 +1824,8 @@
       <c r="C100">
         <v>4</v>
       </c>
-      <c r="E100" t="s">
+      <c/>
+      <c t="s">
         <v>103</v>
       </c>
     </row>
@@ -1744,7 +1839,8 @@
       <c r="C101">
         <v>3.5</v>
       </c>
-      <c r="E101" t="s">
+      <c/>
+      <c t="s">
         <v>104</v>
       </c>
     </row>
@@ -1758,7 +1854,8 @@
       <c r="C102">
         <v>63.03</v>
       </c>
-      <c r="E102" t="s">
+      <c/>
+      <c t="s">
         <v>105</v>
       </c>
     </row>
@@ -1772,7 +1869,8 @@
       <c r="C103">
         <v>19</v>
       </c>
-      <c r="E103" t="s">
+      <c/>
+      <c t="s">
         <v>106</v>
       </c>
     </row>
@@ -1786,7 +1884,8 @@
       <c r="C104">
         <v>17.98</v>
       </c>
-      <c r="E104" t="s">
+      <c/>
+      <c t="s">
         <v>107</v>
       </c>
     </row>
@@ -1800,7 +1899,8 @@
       <c r="C105">
         <v>34.5</v>
       </c>
-      <c r="E105" t="s">
+      <c/>
+      <c t="s">
         <v>108</v>
       </c>
     </row>
